--- a/data/trans_orig/IP19C01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19C01-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17249</t>
+          <t>17259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27332</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37258</t>
+          <t>37740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12678</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37839</t>
+          <t>38680</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48348</t>
+          <t>48531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42952</t>
+          <t>43415</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54120</t>
+          <t>54160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84721</t>
+          <t>84702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99620</t>
+          <t>100078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37476</t>
+          <t>37495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22150</t>
+          <t>22167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20460</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49601</t>
+          <t>48940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>14375</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>20681</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33651</t>
+          <t>33576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21056</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31460</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29354</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37515</t>
+          <t>37547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52559</t>
+          <t>52571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66675</t>
+          <t>66288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31041</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20757</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>27370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37970</t>
+          <t>37512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>21289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27494</t>
+          <t>27264</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38342</t>
+          <t>39084</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>72,78%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>26434</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37970</t>
+          <t>38140</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50098</t>
+          <t>50523</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>38642</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51549</t>
+          <t>50880</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80934</t>
+          <t>80231</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97547</t>
+          <t>97608</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27314</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28670</t>
+          <t>29387</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52380</t>
+          <t>53083</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47713</t>
+          <t>48942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>62239</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44727</t>
+          <t>44876</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56960</t>
+          <t>57266</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96526</t>
+          <t>97811</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115249</t>
+          <t>115091</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33607</t>
+          <t>32378</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29686</t>
+          <t>29537</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40485</t>
+          <t>40643</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59208</t>
+          <t>57923</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>217367</t>
+          <t>216587</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>245325</t>
+          <t>244928</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>244823</t>
+          <t>244598</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>271292</t>
+          <t>271064</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>470225</t>
+          <t>470844</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>509320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105605</t>
+          <t>106002</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>133563</t>
+          <t>134343</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90439</t>
+          <t>90667</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>116908</t>
+          <t>117133</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>201113</t>
+          <t>203341</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>242436</t>
+          <t>241817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19719</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11756</t>
+          <t>11790</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20998</t>
+          <t>21405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>26841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38670</t>
+          <t>38807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12958</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16789</t>
+          <t>16652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29353</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37617</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47254</t>
+          <t>47200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40087</t>
+          <t>40472</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50249</t>
+          <t>50042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81689</t>
+          <t>80992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95105</t>
+          <t>94637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17545</t>
+          <t>17160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>29685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>24460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31511</t>
+          <t>32043</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37555</t>
+          <t>38100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58725</t>
+          <t>58839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68103</t>
+          <t>68091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>14069</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>22205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32567</t>
+          <t>32175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35487</t>
+          <t>34999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50424</t>
+          <t>49401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64405</t>
+          <t>64087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18619</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>33623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18334</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20065</t>
+          <t>20879</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26290</t>
+          <t>26317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41511</t>
+          <t>41589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50168</t>
+          <t>50036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23380</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>31510</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22610</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48400</t>
+          <t>48262</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59467</t>
+          <t>59461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>11893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>40018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52104</t>
+          <t>52132</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47368</t>
+          <t>47658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58506</t>
+          <t>58458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>91655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108624</t>
+          <t>107733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24430</t>
+          <t>23951</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22509</t>
+          <t>23400</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>39392</t>
+          <t>39478</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37932</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51713</t>
+          <t>51518</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39447</t>
+          <t>39052</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51251</t>
+          <t>52257</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>80873</t>
+          <t>80504</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99563</t>
+          <t>98574</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26134</t>
+          <t>26329</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39915</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18836</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30640</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>48371</t>
+          <t>49360</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67061</t>
+          <t>67430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>243057</t>
+          <t>243040</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>269024</t>
+          <t>270963</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>264985</t>
+          <t>264906</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>292453</t>
+          <t>292529</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>516222</t>
+          <t>516752</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>555101</t>
+          <t>553917</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>86997</t>
+          <t>85058</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>112964</t>
+          <t>112981</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74944</t>
+          <t>74868</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>102412</t>
+          <t>102491</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>168317</t>
+          <t>169501</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>207196</t>
+          <t>206666</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20774</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24251</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29855</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42675</t>
+          <t>42371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,88%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18265</t>
+          <t>18225</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18840</t>
+          <t>19144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31660</t>
+          <t>32098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33136</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>44028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34724</t>
+          <t>34523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45853</t>
+          <t>46047</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72507</t>
+          <t>71487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87727</t>
+          <t>87423</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,86%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24045</t>
+          <t>24246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24550</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39770</t>
+          <t>40790</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>22579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24506</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>30745</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49411</t>
+          <t>49208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59420</t>
+          <t>59538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20118</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31232</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32232</t>
+          <t>31701</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43046</t>
+          <t>43022</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56328</t>
+          <t>55929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71955</t>
+          <t>72223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>15329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>26470</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25593</t>
+          <t>25325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41220</t>
+          <t>41619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21107</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>29146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27357</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28805</t>
+          <t>28974</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36934</t>
+          <t>36859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59656</t>
+          <t>59228</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70815</t>
+          <t>70851</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>21085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53111</t>
+          <t>53244</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62452</t>
+          <t>62271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49522</t>
+          <t>48895</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57914</t>
+          <t>57860</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105735</t>
+          <t>105667</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118367</t>
+          <t>117992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,19%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23651</t>
+          <t>23719</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50452</t>
+          <t>50897</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62930</t>
+          <t>63465</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44747</t>
+          <t>45700</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59025</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99321</t>
+          <t>100634</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>118704</t>
+          <t>118846</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17046</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29524</t>
+          <t>29079</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33911</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39787</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59312</t>
+          <t>57999</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>253328</t>
+          <t>254511</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>282120</t>
+          <t>283010</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>267518</t>
+          <t>268115</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>294469</t>
+          <t>294193</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>529969</t>
+          <t>530285</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>569772</t>
+          <t>568634</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>82904</t>
+          <t>82014</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>111696</t>
+          <t>110513</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76933</t>
+          <t>77209</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>103884</t>
+          <t>103287</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>166653</t>
+          <t>167791</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>206456</t>
+          <t>206140</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36261</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71128</t>
+          <t>70798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35209</t>
+          <t>35577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50675</t>
+          <t>51447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39633</t>
+          <t>40339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56678</t>
+          <t>56582</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80818</t>
+          <t>81909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104383</t>
+          <t>105032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18169</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33635</t>
+          <t>33267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>17247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34196</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38290</t>
+          <t>37641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61855</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21180</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28352</t>
+          <t>28303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>29608</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37250</t>
+          <t>37350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53647</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64406</t>
+          <t>64053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18227</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22298</t>
+          <t>22596</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33828</t>
+          <t>34216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34553</t>
+          <t>34163</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52537</t>
+          <t>52508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60562</t>
+          <t>62196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82467</t>
+          <t>83606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24108</t>
+          <t>24498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40942</t>
+          <t>39308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23488</t>
+          <t>23095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31044</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>55597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59492</t>
+          <t>59495</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24377</t>
+          <t>24177</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42992</t>
+          <t>42918</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50625</t>
+          <t>50214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50117</t>
+          <t>50235</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63294</t>
+          <t>63579</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74036</t>
+          <t>74189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91178</t>
+          <t>91532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129732</t>
+          <t>128658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>151232</t>
+          <t>150945</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>17156</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34652</t>
+          <t>34499</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35212</t>
+          <t>35499</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56712</t>
+          <t>57786</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74078</t>
+          <t>73647</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81628</t>
+          <t>81706</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88280</t>
+          <t>88502</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97634</t>
+          <t>97930</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166387</t>
+          <t>165876</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178026</t>
+          <t>178379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18685</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>305727</t>
+          <t>304341</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>332886</t>
+          <t>332207</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>379470</t>
+          <t>381145</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>414420</t>
+          <t>414784</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>694445</t>
+          <t>696742</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>738683</t>
+          <t>739765</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58747</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>85906</t>
+          <t>87292</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>69660</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104974</t>
+          <t>103299</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>137393</t>
+          <t>136311</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>181631</t>
+          <t>179334</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
